--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486533_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486533_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>K. WEBSTER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5001</v>
+        <v>3.1624</v>
       </c>
       <c r="E2" t="n">
-        <v>0.212</v>
+        <v>1.3385</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2882</v>
+        <v>1.824</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.4873</v>
+        <v>0.0275</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2252</v>
+        <v>2.9409</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.7125</v>
+        <v>-2.9133</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.4393</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5316</v>
+        <v>2.9961</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.9076</v>
+        <v>-2.0439</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.048</v>
+        <v>-0.9246</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7568</v>
+        <v>-0.0552</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.8694</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0451</v>
+        <v>2.8276</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6256</v>
+        <v>-0.3001</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2184</v>
+        <v>-0.2211</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4073</v>
+        <v>-0.079</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5958</v>
+        <v>1.695</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5204</v>
+        <v>1.695</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. WEBSTER</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4059</v>
+        <v>1.7566</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7977</v>
+        <v>-1.0928</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6082</v>
+        <v>2.8493</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0275</v>
+        <v>0.0924</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9409</v>
+        <v>-0.9826</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.9133</v>
+        <v>1.075</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.3205</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9961</v>
+        <v>-1.3259</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.0439</v>
+        <v>1.6463</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9246</v>
+        <v>-0.2281</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0552</v>
+        <v>0.3433</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8694</v>
+        <v>-0.5714</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7401</v>
+        <v>-0.435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R3" t="n">
         <v>2.8276</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0566</v>
+        <v>0.435</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7619</v>
+        <v>-0.0408</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2948</v>
+        <v>0.4759</v>
       </c>
       <c r="V3" t="n">
-        <v>1.695</v>
+        <v>1.6642</v>
       </c>
       <c r="W3" t="n">
-        <v>1.695</v>
+        <v>1.8902</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1725</v>
+        <v>0.3207</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6768</v>
+        <v>-0.5415</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8493</v>
+        <v>0.8623</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0924</v>
+        <v>2.0382</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9826</v>
+        <v>0.7114</v>
       </c>
       <c r="I4" t="n">
-        <v>1.075</v>
+        <v>1.3268</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3205</v>
+        <v>1.6455</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3259</v>
+        <v>0.3832</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6463</v>
+        <v>1.2622</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2281</v>
+        <v>0.3927</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3433</v>
+        <v>0.3282</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5714</v>
+        <v>0.0645</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8276</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.149</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6249</v>
+        <v>-0.5552</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4759</v>
+        <v>0.0547</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6642</v>
+        <v>-1.8695</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8902</v>
+        <v>-0.5443</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.226</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.11</v>
+        <v>-0.2251</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4186</v>
+        <v>-1.6194</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5286</v>
+        <v>1.3943</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8733</v>
+        <v>-2.4873</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6448</v>
+        <v>0.2252</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.518</v>
+        <v>-2.7125</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.717</v>
+        <v>-2.4393</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6966</v>
+        <v>-0.5316</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4136</v>
+        <v>-1.9076</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1563</v>
+        <v>-0.048</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0519</v>
+        <v>0.7568</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1044</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>3.0451</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6782</v>
+        <v>0.9004</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6682</v>
+        <v>0.387</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0101</v>
+        <v>0.5134</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5958</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3698</v>
+        <v>1.5204</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>-2.1162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1995</v>
+        <v>-0.3165</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8768</v>
+        <v>-0.6601</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6773</v>
+        <v>0.3437</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0382</v>
+        <v>-0.8733</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7114</v>
+        <v>0.6448</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3268</v>
+        <v>-1.518</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6455</v>
+        <v>-0.717</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3832</v>
+        <v>0.6966</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2622</v>
+        <v>-1.4136</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3927</v>
+        <v>-0.1563</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3282</v>
+        <v>-0.0519</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0645</v>
+        <v>-0.1044</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0207</v>
+        <v>0.2518</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8904</v>
+        <v>0.4266</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1303</v>
+        <v>-0.1749</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8695</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.5443</v>
+        <v>-0.3698</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2749</v>
+        <v>-1.0091</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4438</v>
+        <v>-1.332</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1688</v>
+        <v>0.3229</v>
       </c>
       <c r="G7" t="n">
         <v>0.3503</v>
@@ -1000,13 +1000,13 @@
         <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7553</v>
+        <v>-0.4894</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3443</v>
+        <v>-0.1902</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8263</v>
+        <v>-2.2021</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7192</v>
+        <v>-2.4957</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1071</v>
+        <v>0.2936</v>
       </c>
       <c r="G8" t="n">
         <v>0.951</v>
@@ -1078,13 +1078,13 @@
         <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2999</v>
+        <v>-0.6757</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4779</v>
+        <v>-0.0772</v>
       </c>
       <c r="V8" t="n">
         <v>-2.2599</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9204</v>
+        <v>-2.5098</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1241</v>
+        <v>-2.6518</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2037</v>
+        <v>0.142</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2454</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5997</v>
+        <v>-1.1891</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1644</v>
+        <v>-0.6922</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4353</v>
+        <v>-0.4969</v>
       </c>
       <c r="V9" t="n">
         <v>0.3597</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2226</v>
+        <v>-3.9237</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4192</v>
+        <v>-3.0587</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8034</v>
+        <v>-0.865</v>
       </c>
       <c r="G10" t="n">
         <v>-2.882</v>
@@ -1234,13 +1234,13 @@
         <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5072</v>
+        <v>-1.2083</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0274</v>
+        <v>-0.6669</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4797</v>
+        <v>-0.5414</v>
       </c>
       <c r="V10" t="n">
         <v>-1.356</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.0656</v>
+        <v>-8.3467</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.1913</v>
+        <v>-7.719</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8743</v>
+        <v>-0.6277</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4463</v>
@@ -1312,13 +1312,13 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6081</v>
+        <v>-0.8893</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6934</v>
+        <v>-0.2211</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9147</v>
+        <v>-0.6682</v>
       </c>
       <c r="V11" t="n">
         <v>-0.226</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.3208</v>
+        <v>-13.2933</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.8601</v>
+        <v>-19.8325</v>
       </c>
       <c r="F12" t="n">
-        <v>6.539300000000001</v>
+        <v>6.5394</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.474900000000001</v>
+        <v>-6.4749</v>
       </c>
       <c r="H12" t="n">
         <v>5.8684</v>
@@ -1390,19 +1390,19 @@
         <v>18.4882</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.692699999999999</v>
+        <v>-3.6652</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.5088</v>
+        <v>-2.4813</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1837</v>
+        <v>-1.1838</v>
       </c>
       <c r="V12" t="n">
         <v>-3.1533</v>
       </c>
       <c r="W12" t="n">
-        <v>4.7772</v>
+        <v>4.777200000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-7.930499999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6206</v>
+        <v>5.6719</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6588</v>
+        <v>3.345</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9618</v>
+        <v>2.3269</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7727000000000001</v>
+        <v>4.1523</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8665</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6391</v>
+        <v>3.1548</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4309</v>
+        <v>3.1611</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3341</v>
+        <v>1.4964</v>
       </c>
       <c r="L13" t="n">
-        <v>0.765</v>
+        <v>1.6647</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3417</v>
+        <v>0.9912</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5324</v>
+        <v>-0.4989</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8741</v>
+        <v>1.4901</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1307</v>
+        <v>0.4098</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6427</v>
+        <v>0.1839</v>
       </c>
       <c r="U13" t="n">
-        <v>0.488</v>
+        <v>0.2259</v>
       </c>
       <c r="V13" t="n">
-        <v>2.0647</v>
+        <v>-0.1952</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1745</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5601</v>
+        <v>4.9539</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2332</v>
+        <v>1.653</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3269</v>
+        <v>3.3009</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1523</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9975000000000001</v>
+        <v>-0.8665</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1548</v>
+        <v>1.6391</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1611</v>
+        <v>0.4309</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4964</v>
+        <v>-0.3341</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6647</v>
+        <v>0.765</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9912</v>
+        <v>0.3417</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4989</v>
+        <v>-0.5324</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4901</v>
+        <v>0.8741</v>
       </c>
       <c r="P14" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R14" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>0.298</v>
+        <v>1.464</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0721</v>
+        <v>0.6369</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2259</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1952</v>
+        <v>2.0647</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1952</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0085</v>
+        <v>4.7427</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8246</v>
+        <v>1.7128</v>
       </c>
       <c r="F15" t="n">
-        <v>3.184</v>
+        <v>3.0299</v>
       </c>
       <c r="G15" t="n">
         <v>4.8253</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0533</v>
+        <v>0.7874</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4747</v>
+        <v>0.3629</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5786</v>
+        <v>0.4245</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3783</v>
+        <v>3.1972</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4598</v>
+        <v>0.1245</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9185</v>
+        <v>3.0727</v>
       </c>
       <c r="G16" t="n">
         <v>0.2395</v>
@@ -1702,13 +1702,13 @@
         <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2263</v>
+        <v>1.0452</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4747</v>
+        <v>0.1394</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7516</v>
+        <v>0.9058</v>
       </c>
       <c r="V16" t="n">
         <v>1.695</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4038</v>
+        <v>3.0435</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8784</v>
+        <v>1.549</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5254</v>
+        <v>1.4946</v>
       </c>
       <c r="G17" t="n">
         <v>1.2804</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6166</v>
+        <v>0.0231</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.0829</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1369</v>
+        <v>0.106</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3599</v>
+        <v>1.8147</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0108</v>
+        <v>-0.3403</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3707</v>
+        <v>2.155</v>
       </c>
       <c r="G18" t="n">
         <v>0.4665</v>
@@ -1858,13 +1858,13 @@
         <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9129</v>
+        <v>-0.4581</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1644</v>
+        <v>-0.4939</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2515</v>
+        <v>0.0357</v>
       </c>
       <c r="V18" t="n">
         <v>0.7188</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2295</v>
+        <v>0.7998</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2019</v>
+        <v>-0.7549</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4314</v>
+        <v>1.5547</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8374</v>
@@ -1936,13 +1936,13 @@
         <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8683</v>
+        <v>-0.298</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.536</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3324</v>
+        <v>-0.2091</v>
       </c>
       <c r="V19" t="n">
         <v>0.1952</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3951</v>
+        <v>-0.3257</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.2913</v>
+        <v>-4.0678</v>
       </c>
       <c r="F20" t="n">
-        <v>3.8962</v>
+        <v>3.7421</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7136</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9487</v>
+        <v>1.0181</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1334</v>
+        <v>0.0901</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0821</v>
+        <v>0.928</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1952</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-1.8527</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6429</v>
+        <v>-1.5787</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6827</v>
+        <v>-0.274</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5853</v>
+        <v>-2.5094</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4809</v>
+        <v>-3.2784</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1044</v>
+        <v>0.769</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-2.3842</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-2.597</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.2128</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9013</v>
+        <v>-0.1252</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.6814</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1044</v>
+        <v>0.5562</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1477</v>
+        <v>-0.4308</v>
       </c>
       <c r="T21" t="n">
-        <v>1.4336</v>
+        <v>-0.1069</v>
       </c>
       <c r="U21" t="n">
-        <v>0.714</v>
+        <v>-0.3239</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2611</v>
+        <v>-1.8773</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8022</v>
+        <v>-2.3135</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.459</v>
+        <v>0.4361</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5094</v>
+        <v>-1.5853</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.2784</v>
+        <v>-1.4809</v>
       </c>
       <c r="I22" t="n">
-        <v>0.769</v>
+        <v>-0.1044</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3842</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.597</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2128</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1252</v>
+        <v>-0.9013</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6814</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5562</v>
+        <v>-0.1044</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0875</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8393</v>
+        <v>1.2305</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3305</v>
+        <v>0.7631</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5088</v>
+        <v>0.4675</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6157</v>
+        <v>-2.6543</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3392</v>
+        <v>-3.5627</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7235</v>
+        <v>0.9085</v>
       </c>
       <c r="G23" t="n">
         <v>0.8965</v>
@@ -2248,13 +2248,13 @@
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4454</v>
+        <v>0.4068</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2091</v>
+        <v>-0.0144</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2362</v>
+        <v>0.4212</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.008</v>
+        <v>-3.193</v>
       </c>
       <c r="E24" t="n">
         <v>-2.3058</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7022</v>
+        <v>-0.8872</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5125999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3204</v>
+        <v>-0.5053</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2055</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1149</v>
+        <v>-0.2998</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>14.3206</v>
+        <v>14.3207</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.539300000000001</v>
+        <v>-6.539400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>20.8599</v>
+        <v>20.8602</v>
       </c>
       <c r="G25" t="n">
         <v>6.474900000000001</v>
@@ -2395,7 +2395,7 @@
         <v>7.474299999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>-18.4881</v>
@@ -2404,13 +2404,13 @@
         <v>18.4882</v>
       </c>
       <c r="S25" t="n">
-        <v>4.6926</v>
+        <v>4.692699999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>1.1836</v>
+        <v>1.1838</v>
       </c>
       <c r="U25" t="n">
-        <v>3.508700000000001</v>
+        <v>3.5089</v>
       </c>
       <c r="V25" t="n">
         <v>3.153300000000001</v>
